--- a/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>CCG</t>
   </si>
@@ -656,107 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
-      </c>
-      <c r="G7" s="2">
-        <v>44834</v>
       </c>
       <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>108700</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>456100</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>222500</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>370100</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>160300</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>104100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>436800</v>
+      </c>
+      <c r="F9" s="3">
+        <v>214400</v>
+      </c>
+      <c r="G9" s="3">
+        <v>350500</v>
+      </c>
+      <c r="H9" s="3">
+        <v>151300</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>4</v>
@@ -767,25 +781,31 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>19700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>9000</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>4</v>
@@ -796,8 +816,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,25 +835,27 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
+      <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3200</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>4</v>
@@ -838,8 +866,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +901,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -876,28 +916,34 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-2800</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-1500</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +971,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +987,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>400</v>
+        <v>113100</v>
       </c>
       <c r="E17" s="3">
-        <v>1300</v>
+        <v>477600</v>
       </c>
       <c r="F17" s="3">
-        <v>900</v>
+        <v>231200</v>
       </c>
       <c r="G17" s="3">
-        <v>800</v>
+        <v>383400</v>
       </c>
       <c r="H17" s="3">
+        <v>168600</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3">
+        <v>300</v>
+      </c>
+      <c r="L17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3">
-        <v>300</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-4400</v>
       </c>
       <c r="E18" s="3">
-        <v>-1300</v>
+        <v>-21500</v>
       </c>
       <c r="F18" s="3">
-        <v>-900</v>
+        <v>-8700</v>
       </c>
       <c r="G18" s="3">
-        <v>-800</v>
+        <v>-13200</v>
       </c>
       <c r="H18" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,37 +1072,45 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
-        <v>1100</v>
+        <v>-1200</v>
       </c>
       <c r="G20" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H20" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2700</v>
+        <v>200</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M20" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1049,11 +1123,11 @@
       <c r="F21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
+      <c r="G21" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-7900</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
@@ -1064,8 +1138,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1073,57 +1153,69 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E23" s="3">
-        <v>-1300</v>
+        <v>-22100</v>
       </c>
       <c r="F23" s="3">
-        <v>200</v>
+        <v>-10000</v>
       </c>
       <c r="G23" s="3">
-        <v>300</v>
+        <v>-12600</v>
       </c>
       <c r="H23" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="3">
         <v>4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1131,28 +1223,34 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1278,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E26" s="3">
-        <v>-1300</v>
+        <v>-22000</v>
       </c>
       <c r="F26" s="3">
-        <v>200</v>
+        <v>-10000</v>
       </c>
       <c r="G26" s="3">
-        <v>300</v>
+        <v>-12600</v>
       </c>
       <c r="H26" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I26" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3">
         <v>4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E27" s="3">
-        <v>-1300</v>
+        <v>-127400</v>
       </c>
       <c r="F27" s="3">
-        <v>200</v>
+        <v>-25200</v>
       </c>
       <c r="G27" s="3">
-        <v>300</v>
+        <v>-38600</v>
       </c>
       <c r="H27" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I27" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1383,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1418,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1453,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1488,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
-        <v>-1100</v>
+        <v>1200</v>
       </c>
       <c r="G32" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="H32" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2700</v>
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>-5000</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E33" s="3">
-        <v>-1300</v>
+        <v>-127400</v>
       </c>
       <c r="F33" s="3">
-        <v>200</v>
+        <v>-25200</v>
       </c>
       <c r="G33" s="3">
-        <v>300</v>
+        <v>-38600</v>
       </c>
       <c r="H33" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I33" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1593,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E35" s="3">
-        <v>-1300</v>
+        <v>-127400</v>
       </c>
       <c r="F35" s="3">
-        <v>200</v>
+        <v>-25200</v>
       </c>
       <c r="G35" s="3">
-        <v>300</v>
+        <v>-38600</v>
       </c>
       <c r="H35" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I35" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
-      </c>
-      <c r="G38" s="2">
-        <v>44834</v>
       </c>
       <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1687,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,95 +1702,115 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>30300</v>
       </c>
       <c r="E41" s="3">
-        <v>400</v>
+        <v>33600</v>
       </c>
       <c r="F41" s="3">
-        <v>100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>200</v>
-      </c>
-      <c r="H41" s="3">
-        <v>500</v>
-      </c>
-      <c r="I41" s="3">
+        <v>20700</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>66800</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>69900</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>64100</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1646,153 +1838,189 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
+        <v>2100</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>100</v>
+      </c>
+      <c r="M45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>100</v>
+        <v>106100</v>
       </c>
       <c r="E46" s="3">
-        <v>500</v>
+        <v>107800</v>
       </c>
       <c r="F46" s="3">
-        <v>100</v>
-      </c>
-      <c r="G46" s="3">
-        <v>300</v>
-      </c>
-      <c r="H46" s="3">
-        <v>500</v>
-      </c>
-      <c r="I46" s="3">
+        <v>89000</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>48500</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>69800</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>69400</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>324700</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>324200</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>324200</v>
+        <v>0</v>
       </c>
       <c r="K47" s="3">
         <v>324200</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>324200</v>
+      </c>
+      <c r="M47" s="3">
+        <v>324200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>1700</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>12900</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2048,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +2083,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>1300</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2153,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>49600</v>
+        <v>121800</v>
       </c>
       <c r="E54" s="3">
-        <v>49000</v>
+        <v>123500</v>
       </c>
       <c r="F54" s="3">
-        <v>69900</v>
-      </c>
-      <c r="G54" s="3">
-        <v>69700</v>
-      </c>
-      <c r="H54" s="3">
-        <v>325200</v>
-      </c>
-      <c r="I54" s="3">
+        <v>103600</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>324900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>325000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>325100</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2207,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,51 +2222,59 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>700</v>
+        <v>44500</v>
       </c>
       <c r="E57" s="3">
-        <v>900</v>
+        <v>43800</v>
       </c>
       <c r="F57" s="3">
-        <v>800</v>
-      </c>
-      <c r="G57" s="3">
+        <v>38800</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
+        <v>500</v>
+      </c>
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
-        <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>500</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3500</v>
+        <v>2300</v>
       </c>
       <c r="E58" s="3">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="F58" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1100</v>
+        <v>2800</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
@@ -2020,66 +2288,84 @@
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2400</v>
+        <v>22700</v>
       </c>
       <c r="E59" s="3">
-        <v>2100</v>
+        <v>22800</v>
       </c>
       <c r="F59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>900</v>
-      </c>
-      <c r="H59" s="3">
+        <v>15200</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
-        <v>200</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6600</v>
+        <v>69500</v>
       </c>
       <c r="E60" s="3">
-        <v>6000</v>
+        <v>69300</v>
       </c>
       <c r="F60" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>600</v>
-      </c>
-      <c r="I60" s="3">
+        <v>56800</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2107,37 +2393,49 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>700</v>
+        <v>1900</v>
       </c>
       <c r="E62" s="3">
-        <v>700</v>
+        <v>2000</v>
       </c>
       <c r="F62" s="3">
-        <v>300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>12300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>12300</v>
-      </c>
-      <c r="I62" s="3">
+        <v>9900</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>15300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>20300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2463,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2498,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2533,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7200</v>
+        <v>71400</v>
       </c>
       <c r="E66" s="3">
-        <v>6700</v>
+        <v>71300</v>
       </c>
       <c r="F66" s="3">
-        <v>3800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>14600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>13000</v>
-      </c>
-      <c r="I66" s="3">
+        <v>66700</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>16000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>20800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2587,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2618,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2653,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2335,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>230600</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -2352,8 +2688,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2723,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-7000</v>
+        <v>-296400</v>
       </c>
       <c r="E72" s="3">
-        <v>-6100</v>
+        <v>-292000</v>
       </c>
       <c r="F72" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-14300</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="I72" s="3">
+        <v>-194500</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-15200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-19900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-22400</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2793,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2828,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2863,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>42400</v>
+        <v>50400</v>
       </c>
       <c r="E76" s="3">
-        <v>42300</v>
+        <v>52200</v>
       </c>
       <c r="F76" s="3">
-        <v>66100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>55000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>312200</v>
-      </c>
-      <c r="I76" s="3">
+        <v>-193700</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>308900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>304200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>301700</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2933,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
-      </c>
-      <c r="G80" s="2">
-        <v>44834</v>
       </c>
       <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="I80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E81" s="3">
-        <v>-1300</v>
+        <v>-127400</v>
       </c>
       <c r="F81" s="3">
-        <v>200</v>
+        <v>-25200</v>
       </c>
       <c r="G81" s="3">
-        <v>300</v>
+        <v>-38600</v>
       </c>
       <c r="H81" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I81" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +3027,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3093,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3128,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3163,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3198,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3233,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-100</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+        <v>-21900</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,16 +3287,18 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -2876,8 +3318,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3353,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,22 +3388,28 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="E94" s="3">
-        <v>21500</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3">
+        <v>3800</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
@@ -2963,8 +3423,14 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3442,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3473,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3508,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3543,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,22 +3578,28 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>500</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-20900</v>
-      </c>
-      <c r="F100" s="3">
-        <v>400</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G100" s="3">
-        <v>-256400</v>
+        <v>-22000</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
@@ -3115,68 +3607,86 @@
       <c r="I100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+        <v>5900</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="E102" s="3">
-        <v>300</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-100</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+        <v>-34200</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
   <si>
     <t>CCG</t>
   </si>
@@ -656,95 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>108700</v>
+        <v>120100</v>
       </c>
       <c r="E8" s="3">
-        <v>456100</v>
+        <v>111000</v>
       </c>
       <c r="F8" s="3">
-        <v>222500</v>
+        <v>465400</v>
       </c>
       <c r="G8" s="3">
-        <v>370100</v>
+        <v>227000</v>
       </c>
       <c r="H8" s="3">
-        <v>160300</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
+        <v>377700</v>
+      </c>
+      <c r="I8" s="3">
+        <v>163600</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -752,28 +756,31 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>104100</v>
+        <v>115700</v>
       </c>
       <c r="E9" s="3">
-        <v>436800</v>
+        <v>106200</v>
       </c>
       <c r="F9" s="3">
-        <v>214400</v>
+        <v>445700</v>
       </c>
       <c r="G9" s="3">
-        <v>350500</v>
+        <v>218800</v>
       </c>
       <c r="H9" s="3">
-        <v>151300</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
+        <v>357600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>154400</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>4</v>
@@ -787,28 +794,31 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>4700</v>
+        <v>4400</v>
       </c>
       <c r="E10" s="3">
-        <v>19400</v>
+        <v>4800</v>
       </c>
       <c r="F10" s="3">
-        <v>8100</v>
+        <v>19800</v>
       </c>
       <c r="G10" s="3">
-        <v>19700</v>
+        <v>8200</v>
       </c>
       <c r="H10" s="3">
-        <v>9000</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
+        <v>20100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>9200</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>4</v>
@@ -822,8 +832,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +850,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,19 +860,19 @@
         <v>1300</v>
       </c>
       <c r="E12" s="3">
-        <v>7900</v>
+        <v>1300</v>
       </c>
       <c r="F12" s="3">
-        <v>4300</v>
+        <v>8100</v>
       </c>
       <c r="G12" s="3">
-        <v>6900</v>
+        <v>4400</v>
       </c>
       <c r="H12" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
+        <v>7000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3300</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
@@ -872,8 +886,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +924,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -916,25 +936,25 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-2800</v>
-      </c>
       <c r="H14" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+        <v>-2900</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-1600</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -942,8 +962,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1015,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>113100</v>
+        <v>123700</v>
       </c>
       <c r="E17" s="3">
-        <v>477600</v>
+        <v>115400</v>
       </c>
       <c r="F17" s="3">
-        <v>231200</v>
+        <v>487300</v>
       </c>
       <c r="G17" s="3">
-        <v>383400</v>
+        <v>235900</v>
       </c>
       <c r="H17" s="3">
-        <v>168600</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>4</v>
+        <v>391200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>172100</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L17" s="3">
         <v>300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>100</v>
       </c>
       <c r="M17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4400</v>
+        <v>-3600</v>
       </c>
       <c r="E18" s="3">
-        <v>-21500</v>
+        <v>-4500</v>
       </c>
       <c r="F18" s="3">
-        <v>-8700</v>
+        <v>-21900</v>
       </c>
       <c r="G18" s="3">
-        <v>-13200</v>
+        <v>-8900</v>
       </c>
       <c r="H18" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
+        <v>-13500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-8500</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>-300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-100</v>
       </c>
       <c r="M18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,43 +1107,47 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>5000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1120,17 +1157,17 @@
       <c r="E21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
+      <c r="F21" s="3">
+        <v>-21900</v>
       </c>
       <c r="G21" s="3">
-        <v>-11700</v>
+        <v>-9900</v>
       </c>
       <c r="H21" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
+        <v>-12000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-8000</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
@@ -1144,8 +1181,11 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1153,25 +1193,25 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1179,43 +1219,49 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-4300</v>
+        <v>-3300</v>
       </c>
       <c r="E23" s="3">
-        <v>-22100</v>
+        <v>-4400</v>
       </c>
       <c r="F23" s="3">
-        <v>-10000</v>
+        <v>-22600</v>
       </c>
       <c r="G23" s="3">
-        <v>-12600</v>
+        <v>-10200</v>
       </c>
       <c r="H23" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>4</v>
+        <v>-12900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-8600</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23" s="3">
         <v>4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1223,25 +1269,25 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1249,8 +1295,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1333,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-4300</v>
+        <v>-3300</v>
       </c>
       <c r="E26" s="3">
-        <v>-22000</v>
+        <v>-4400</v>
       </c>
       <c r="F26" s="3">
-        <v>-10000</v>
+        <v>-22500</v>
       </c>
       <c r="G26" s="3">
-        <v>-12600</v>
+        <v>-10200</v>
       </c>
       <c r="H26" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>4</v>
+        <v>-12800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-8600</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="3">
         <v>4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4300</v>
+        <v>-3300</v>
       </c>
       <c r="E27" s="3">
-        <v>-127400</v>
+        <v>-4400</v>
       </c>
       <c r="F27" s="3">
-        <v>-25200</v>
+        <v>-129900</v>
       </c>
       <c r="G27" s="3">
-        <v>-38600</v>
+        <v>-25700</v>
       </c>
       <c r="H27" s="3">
-        <v>-17700</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>4</v>
+        <v>-39400</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-18100</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27" s="3">
         <v>4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1447,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,78 +1561,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-5000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-4300</v>
+        <v>-3300</v>
       </c>
       <c r="E33" s="3">
-        <v>-127400</v>
+        <v>-4400</v>
       </c>
       <c r="F33" s="3">
-        <v>-25200</v>
+        <v>-129900</v>
       </c>
       <c r="G33" s="3">
-        <v>-38600</v>
+        <v>-25700</v>
       </c>
       <c r="H33" s="3">
-        <v>-17700</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>4</v>
+        <v>-39400</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-18100</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L33" s="3">
         <v>4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1675,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-4300</v>
+        <v>-3300</v>
       </c>
       <c r="E35" s="3">
-        <v>-127400</v>
+        <v>-4400</v>
       </c>
       <c r="F35" s="3">
-        <v>-25200</v>
+        <v>-129900</v>
       </c>
       <c r="G35" s="3">
-        <v>-38600</v>
+        <v>-25700</v>
       </c>
       <c r="H35" s="3">
-        <v>-17700</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>4</v>
+        <v>-39400</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-18100</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L35" s="3">
         <v>4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,22 +1790,23 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>30300</v>
+        <v>18800</v>
       </c>
       <c r="E41" s="3">
-        <v>33600</v>
+        <v>31000</v>
       </c>
       <c r="F41" s="3">
-        <v>20700</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
+        <v>34300</v>
+      </c>
+      <c r="G41" s="3">
+        <v>21100</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>4</v>
@@ -1730,32 +1817,35 @@
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>600</v>
-      </c>
-      <c r="L41" s="3">
-        <v>700</v>
       </c>
       <c r="M41" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E42" s="3">
         <v>2000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2000</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>4</v>
       </c>
@@ -1765,8 +1855,8 @@
       <c r="J42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -1774,22 +1864,25 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>66800</v>
+        <v>90100</v>
       </c>
       <c r="E43" s="3">
-        <v>69900</v>
+        <v>68200</v>
       </c>
       <c r="F43" s="3">
-        <v>64100</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
+        <v>71300</v>
+      </c>
+      <c r="G43" s="3">
+        <v>65400</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
@@ -1800,8 +1893,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1809,8 +1902,11 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1844,22 +1940,25 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7000</v>
+        <v>7500</v>
       </c>
       <c r="E45" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
+      <c r="G45" s="3">
+        <v>2200</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
@@ -1870,8 +1969,8 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>100</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>100</v>
@@ -1879,22 +1978,25 @@
       <c r="M45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>106100</v>
+        <v>126400</v>
       </c>
       <c r="E46" s="3">
-        <v>107800</v>
+        <v>108300</v>
       </c>
       <c r="F46" s="3">
-        <v>89000</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
+        <v>110000</v>
+      </c>
+      <c r="G46" s="3">
+        <v>90800</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>4</v>
@@ -1905,17 +2007,20 @@
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1941,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
-        <v>324200</v>
+        <v>0</v>
       </c>
       <c r="L47" s="3">
         <v>324200</v>
@@ -1949,22 +2054,25 @@
       <c r="M47" s="3">
         <v>324200</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>324200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1700</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1600</v>
       </c>
       <c r="F48" s="3">
         <v>1700</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
+      <c r="G48" s="3">
+        <v>1700</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>4</v>
@@ -1975,8 +2083,8 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -1984,22 +2092,25 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>12700</v>
+        <v>12900</v>
       </c>
       <c r="E49" s="3">
-        <v>12800</v>
+        <v>13000</v>
       </c>
       <c r="F49" s="3">
-        <v>12900</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
+        <v>13100</v>
+      </c>
+      <c r="G49" s="3">
+        <v>13200</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>4</v>
@@ -2010,8 +2121,8 @@
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2019,8 +2130,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,8 +2206,11 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2100,8 +2220,8 @@
       <c r="E52" s="3">
         <v>1300</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
+      <c r="F52" s="3">
+        <v>1300</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
@@ -2115,8 +2235,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2124,8 +2244,11 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,22 +2282,25 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>121800</v>
+        <v>142400</v>
       </c>
       <c r="E54" s="3">
-        <v>123500</v>
+        <v>124300</v>
       </c>
       <c r="F54" s="3">
-        <v>103600</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
+        <v>126000</v>
+      </c>
+      <c r="G54" s="3">
+        <v>105700</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>4</v>
@@ -2185,17 +2311,20 @@
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>324900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>325000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>325100</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,22 +2354,23 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>44500</v>
+        <v>65900</v>
       </c>
       <c r="E57" s="3">
-        <v>43800</v>
+        <v>45400</v>
       </c>
       <c r="F57" s="3">
-        <v>38800</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
+        <v>44700</v>
+      </c>
+      <c r="G57" s="3">
+        <v>39600</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>4</v>
@@ -2250,31 +2381,34 @@
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
         <v>500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>300</v>
       </c>
       <c r="M57" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
+      <c r="G58" s="3">
+        <v>2800</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
@@ -2294,22 +2428,25 @@
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>22700</v>
+        <v>23200</v>
       </c>
       <c r="E59" s="3">
-        <v>22800</v>
+        <v>23200</v>
       </c>
       <c r="F59" s="3">
-        <v>15200</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
+        <v>23200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>15500</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>4</v>
@@ -2320,31 +2457,34 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
-        <v>200</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>200</v>
       </c>
       <c r="M59" s="3">
+        <v>200</v>
+      </c>
+      <c r="N59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>69500</v>
+        <v>91200</v>
       </c>
       <c r="E60" s="3">
-        <v>69300</v>
+        <v>71000</v>
       </c>
       <c r="F60" s="3">
-        <v>56800</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
+        <v>70700</v>
+      </c>
+      <c r="G60" s="3">
+        <v>58000</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>4</v>
@@ -2355,17 +2495,20 @@
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2399,22 +2542,25 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
-        <v>9900</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
+      <c r="G62" s="3">
+        <v>10100</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>4</v>
@@ -2425,17 +2571,20 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>15300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,22 +2694,25 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>71400</v>
+        <v>92700</v>
       </c>
       <c r="E66" s="3">
-        <v>71300</v>
+        <v>72900</v>
       </c>
       <c r="F66" s="3">
-        <v>66700</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
+        <v>72700</v>
+      </c>
+      <c r="G66" s="3">
+        <v>68100</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>4</v>
@@ -2565,17 +2723,20 @@
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>16000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2671,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>230600</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>235300</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,22 +2900,25 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-296400</v>
+        <v>-305700</v>
       </c>
       <c r="E72" s="3">
-        <v>-292000</v>
+        <v>-302400</v>
       </c>
       <c r="F72" s="3">
-        <v>-194500</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
+        <v>-298000</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-198500</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>4</v>
@@ -2755,17 +2929,20 @@
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-15200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-19900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-22400</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,22 +3052,25 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>50400</v>
+        <v>49700</v>
       </c>
       <c r="E76" s="3">
-        <v>52200</v>
+        <v>51400</v>
       </c>
       <c r="F76" s="3">
-        <v>-193700</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
+        <v>53300</v>
+      </c>
+      <c r="G76" s="3">
+        <v>-197600</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>4</v>
@@ -2895,17 +3081,20 @@
       <c r="J76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>308900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>304200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>301700</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3128,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-4300</v>
+        <v>-3300</v>
       </c>
       <c r="E81" s="3">
-        <v>-127400</v>
+        <v>-4400</v>
       </c>
       <c r="F81" s="3">
-        <v>-25200</v>
+        <v>-129900</v>
       </c>
       <c r="G81" s="3">
-        <v>-38600</v>
+        <v>-25700</v>
       </c>
       <c r="H81" s="3">
-        <v>-17700</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>4</v>
+        <v>-39400</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-18100</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L81" s="3">
         <v>4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,8 +3227,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3040,11 +3239,11 @@
       <c r="E83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
+      <c r="F83" s="3">
+        <v>400</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>4</v>
@@ -3055,8 +3254,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3064,8 +3263,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,8 +3453,11 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3250,11 +3467,11 @@
       <c r="E89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>4</v>
+      <c r="F89" s="3">
+        <v>-3800</v>
       </c>
       <c r="G89" s="3">
-        <v>-21900</v>
+        <v>-1100</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>4</v>
@@ -3265,8 +3482,8 @@
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -3274,8 +3491,11 @@
       <c r="M89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,8 +3509,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3298,7 +3519,7 @@
         <v>-400</v>
       </c>
       <c r="E91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -3324,8 +3545,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,8 +3621,11 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3405,11 +3635,11 @@
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
+      <c r="F94" s="3">
+        <v>1800</v>
       </c>
       <c r="G94" s="3">
-        <v>3800</v>
+        <v>2800</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
@@ -3429,8 +3659,11 @@
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3677,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3479,8 +3713,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,8 +3827,11 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3595,11 +3841,11 @@
       <c r="E100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
+      <c r="F100" s="3">
+        <v>19800</v>
       </c>
       <c r="G100" s="3">
-        <v>-22000</v>
+        <v>2800</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
@@ -3613,14 +3859,17 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3630,11 +3879,11 @@
       <c r="E101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>4</v>
+      <c r="F101" s="3">
+        <v>300</v>
       </c>
       <c r="G101" s="3">
-        <v>5900</v>
+        <v>300</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>4</v>
@@ -3645,8 +3894,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3654,8 +3903,11 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3665,11 +3917,11 @@
       <c r="E102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>4</v>
+      <c r="F102" s="3">
+        <v>18100</v>
       </c>
       <c r="G102" s="3">
-        <v>-34200</v>
+        <v>4900</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>4</v>
@@ -3680,13 +3932,16 @@
       <c r="J102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>CCG</t>
   </si>
@@ -656,102 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
-        <v>44926</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>4</v>
+      <c r="J7" s="2">
+        <v>45016</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>120100</v>
+        <v>121300</v>
       </c>
       <c r="E8" s="3">
-        <v>111000</v>
+        <v>117200</v>
       </c>
       <c r="F8" s="3">
-        <v>465400</v>
+        <v>109000</v>
       </c>
       <c r="G8" s="3">
-        <v>227000</v>
+        <v>122400</v>
       </c>
       <c r="H8" s="3">
-        <v>377700</v>
+        <v>112800</v>
       </c>
       <c r="I8" s="3">
-        <v>163600</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
+        <v>114500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>113500</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -759,31 +762,34 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>115700</v>
+        <v>115200</v>
       </c>
       <c r="E9" s="3">
-        <v>106200</v>
+        <v>112800</v>
       </c>
       <c r="F9" s="3">
-        <v>445700</v>
+        <v>104300</v>
       </c>
       <c r="G9" s="3">
-        <v>218800</v>
+        <v>116300</v>
       </c>
       <c r="H9" s="3">
-        <v>357600</v>
+        <v>107600</v>
       </c>
       <c r="I9" s="3">
-        <v>154400</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+        <v>111000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>108600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -797,31 +803,34 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E10" s="3">
         <v>4400</v>
       </c>
-      <c r="E10" s="3">
-        <v>4800</v>
-      </c>
       <c r="F10" s="3">
-        <v>19800</v>
+        <v>4700</v>
       </c>
       <c r="G10" s="3">
-        <v>8200</v>
+        <v>6100</v>
       </c>
       <c r="H10" s="3">
-        <v>20100</v>
+        <v>5300</v>
       </c>
       <c r="I10" s="3">
-        <v>9200</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+        <v>3500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -835,8 +844,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,31 +863,32 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E12" s="3">
         <v>1300</v>
       </c>
       <c r="F12" s="3">
-        <v>8100</v>
+        <v>1300</v>
       </c>
       <c r="G12" s="3">
-        <v>4400</v>
+        <v>1700</v>
       </c>
       <c r="H12" s="3">
-        <v>7000</v>
+        <v>1800</v>
       </c>
       <c r="I12" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
+        <v>1600</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2900</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
@@ -889,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,28 +943,31 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-1600</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
@@ -956,8 +975,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -965,31 +984,34 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1003,8 +1025,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>123700</v>
+        <v>122100</v>
       </c>
       <c r="E17" s="3">
-        <v>115400</v>
+        <v>120700</v>
       </c>
       <c r="F17" s="3">
-        <v>487300</v>
+        <v>113400</v>
       </c>
       <c r="G17" s="3">
-        <v>235900</v>
+        <v>129200</v>
       </c>
       <c r="H17" s="3">
-        <v>391200</v>
+        <v>119500</v>
       </c>
       <c r="I17" s="3">
-        <v>172100</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>4</v>
+        <v>117800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>120300</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3">
         <v>300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>100</v>
       </c>
       <c r="N17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3600</v>
+        <v>-900</v>
       </c>
       <c r="E18" s="3">
-        <v>-4500</v>
+        <v>-3500</v>
       </c>
       <c r="F18" s="3">
-        <v>-21900</v>
+        <v>-4400</v>
       </c>
       <c r="G18" s="3">
-        <v>-8900</v>
+        <v>-6900</v>
       </c>
       <c r="H18" s="3">
-        <v>-13500</v>
+        <v>-6700</v>
       </c>
       <c r="I18" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
+        <v>-3200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-6800</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-100</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,69 +1140,73 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>-1200</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>800</v>
+      </c>
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3300</v>
       </c>
       <c r="F21" s="3">
-        <v>-21900</v>
+        <v>-4500</v>
       </c>
       <c r="G21" s="3">
-        <v>-9900</v>
+        <v>-4700</v>
       </c>
       <c r="H21" s="3">
-        <v>-12000</v>
+        <v>-7600</v>
       </c>
       <c r="I21" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>-3900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-6300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1184,8 +1220,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1196,25 +1235,25 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>400</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1222,46 +1261,52 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3300</v>
       </c>
-      <c r="E23" s="3">
-        <v>-4400</v>
-      </c>
       <c r="F23" s="3">
-        <v>-22600</v>
+        <v>-4300</v>
       </c>
       <c r="G23" s="3">
-        <v>-10200</v>
+        <v>-4500</v>
       </c>
       <c r="H23" s="3">
-        <v>-12900</v>
+        <v>-7600</v>
       </c>
       <c r="I23" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>4</v>
+        <v>-3900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-6400</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3">
         <v>4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1272,25 +1317,25 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1298,8 +1343,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3300</v>
+        <v>600</v>
       </c>
       <c r="E26" s="3">
-        <v>-4400</v>
+        <v>-3200</v>
       </c>
       <c r="F26" s="3">
-        <v>-22500</v>
+        <v>-4300</v>
       </c>
       <c r="G26" s="3">
-        <v>-10200</v>
+        <v>-4500</v>
       </c>
       <c r="H26" s="3">
-        <v>-12800</v>
+        <v>-7600</v>
       </c>
       <c r="I26" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>4</v>
+        <v>-3900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-6400</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3">
         <v>4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3300</v>
+        <v>600</v>
       </c>
       <c r="E27" s="3">
-        <v>-4400</v>
+        <v>-3200</v>
       </c>
       <c r="F27" s="3">
-        <v>-129900</v>
+        <v>-4300</v>
       </c>
       <c r="G27" s="3">
-        <v>-25700</v>
+        <v>-4500</v>
       </c>
       <c r="H27" s="3">
-        <v>-39400</v>
+        <v>-97000</v>
       </c>
       <c r="I27" s="3">
-        <v>-18100</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>4</v>
+        <v>-16200</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-9400</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3">
         <v>4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>1200</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3300</v>
+        <v>600</v>
       </c>
       <c r="E33" s="3">
-        <v>-4400</v>
+        <v>-3200</v>
       </c>
       <c r="F33" s="3">
-        <v>-129900</v>
+        <v>-4300</v>
       </c>
       <c r="G33" s="3">
-        <v>-25700</v>
+        <v>-4500</v>
       </c>
       <c r="H33" s="3">
-        <v>-39400</v>
+        <v>-7600</v>
       </c>
       <c r="I33" s="3">
-        <v>-18100</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>4</v>
+        <v>-3900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-6400</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3">
         <v>4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3300</v>
+        <v>600</v>
       </c>
       <c r="E35" s="3">
-        <v>-4400</v>
+        <v>-3200</v>
       </c>
       <c r="F35" s="3">
-        <v>-129900</v>
+        <v>-4300</v>
       </c>
       <c r="G35" s="3">
-        <v>-25700</v>
+        <v>-4500</v>
       </c>
       <c r="H35" s="3">
-        <v>-39400</v>
+        <v>-7600</v>
       </c>
       <c r="I35" s="3">
-        <v>-18100</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>4</v>
+        <v>-3900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-6400</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3">
         <v>4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
-        <v>44926</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>4</v>
+      <c r="J38" s="2">
+        <v>45016</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,28 +1876,29 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>18800</v>
+        <v>18700</v>
       </c>
       <c r="E41" s="3">
-        <v>31000</v>
+        <v>18300</v>
       </c>
       <c r="F41" s="3">
+        <v>30400</v>
+      </c>
+      <c r="G41" s="3">
         <v>34300</v>
       </c>
-      <c r="G41" s="3">
-        <v>21100</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
+      <c r="H41" s="3">
+        <v>35700</v>
+      </c>
+      <c r="I41" s="3">
+        <v>20700</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
@@ -1820,46 +1906,49 @@
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>600</v>
-      </c>
-      <c r="M41" s="3">
-        <v>700</v>
       </c>
       <c r="N41" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>10100</v>
+        <v>9100</v>
       </c>
       <c r="E42" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F42" s="3">
         <v>2000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2000</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
+      <c r="I42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1867,28 +1956,31 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>90100</v>
+        <v>106500</v>
       </c>
       <c r="E43" s="3">
-        <v>68200</v>
+        <v>89300</v>
       </c>
       <c r="F43" s="3">
-        <v>71300</v>
+        <v>67000</v>
       </c>
       <c r="G43" s="3">
-        <v>65400</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
+        <v>65700</v>
+      </c>
+      <c r="H43" s="3">
+        <v>61100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>59100</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
@@ -1896,8 +1988,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -1905,31 +1997,34 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1943,28 +2038,31 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="E45" s="3">
-        <v>7100</v>
+        <v>4600</v>
       </c>
       <c r="F45" s="3">
-        <v>1300</v>
+        <v>7000</v>
       </c>
       <c r="G45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+        <v>6200</v>
+      </c>
+      <c r="H45" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>5700</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
@@ -1972,8 +2070,8 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>100</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
@@ -1981,28 +2079,31 @@
       <c r="N45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>126400</v>
+        <v>140200</v>
       </c>
       <c r="E46" s="3">
-        <v>108300</v>
+        <v>123400</v>
       </c>
       <c r="F46" s="3">
+        <v>106400</v>
+      </c>
+      <c r="G46" s="3">
         <v>110000</v>
       </c>
-      <c r="G46" s="3">
-        <v>90800</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
+      <c r="H46" s="3">
+        <v>106300</v>
+      </c>
+      <c r="I46" s="3">
+        <v>88800</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
@@ -2010,46 +2111,49 @@
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
       <c r="L47" s="3">
-        <v>324200</v>
+        <v>0</v>
       </c>
       <c r="M47" s="3">
         <v>324200</v>
@@ -2057,13 +2161,16 @@
       <c r="N47" s="3">
         <v>324200</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>324200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="E48" s="3">
         <v>1700</v>
@@ -2074,11 +2181,11 @@
       <c r="G48" s="3">
         <v>1700</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
+      <c r="H48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1700</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>4</v>
@@ -2086,8 +2193,8 @@
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2095,37 +2202,40 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F49" s="3">
+        <v>12800</v>
+      </c>
+      <c r="G49" s="3">
+        <v>13100</v>
+      </c>
+      <c r="H49" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I49" s="3">
         <v>12900</v>
       </c>
-      <c r="E49" s="3">
-        <v>13000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>13100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>13200</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2133,8 +2243,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,22 +2325,25 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E52" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F52" s="3">
         <v>1300</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
+      <c r="G52" s="3">
+        <v>1300</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>4</v>
@@ -2238,8 +2357,8 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2247,8 +2366,11 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,28 +2407,31 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>142400</v>
+        <v>156200</v>
       </c>
       <c r="E54" s="3">
-        <v>124300</v>
+        <v>139000</v>
       </c>
       <c r="F54" s="3">
-        <v>126000</v>
+        <v>122100</v>
       </c>
       <c r="G54" s="3">
-        <v>105700</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
+        <v>126100</v>
+      </c>
+      <c r="H54" s="3">
+        <v>120500</v>
+      </c>
+      <c r="I54" s="3">
+        <v>103400</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
@@ -2314,17 +2439,20 @@
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>324900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>325000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>325100</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,28 +2484,29 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>65900</v>
+        <v>80700</v>
       </c>
       <c r="E57" s="3">
-        <v>45400</v>
+        <v>64300</v>
       </c>
       <c r="F57" s="3">
+        <v>44600</v>
+      </c>
+      <c r="G57" s="3">
         <v>44700</v>
       </c>
-      <c r="G57" s="3">
-        <v>39600</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
+      <c r="H57" s="3">
+        <v>38400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>38800</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
@@ -2384,40 +2514,43 @@
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>500</v>
-      </c>
-      <c r="M57" s="3">
-        <v>300</v>
       </c>
       <c r="N57" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2100</v>
+        <v>2700</v>
       </c>
       <c r="E58" s="3">
-        <v>2400</v>
+        <v>10800</v>
       </c>
       <c r="F58" s="3">
-        <v>2800</v>
+        <v>10900</v>
       </c>
       <c r="G58" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+        <v>11200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
@@ -2431,28 +2564,31 @@
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>23200</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
-        <v>23200</v>
+        <v>1700</v>
       </c>
       <c r="F59" s="3">
-        <v>23200</v>
+        <v>600</v>
       </c>
       <c r="G59" s="3">
-        <v>15500</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+        <v>2000</v>
+      </c>
+      <c r="H59" s="3">
+        <v>900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1300</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
@@ -2460,37 +2596,40 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
-        <v>200</v>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M59" s="3">
         <v>200</v>
       </c>
       <c r="N59" s="3">
+        <v>200</v>
+      </c>
+      <c r="O59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>91200</v>
+        <v>98200</v>
       </c>
       <c r="E60" s="3">
-        <v>71000</v>
+        <v>89000</v>
       </c>
       <c r="F60" s="3">
+        <v>69700</v>
+      </c>
+      <c r="G60" s="3">
         <v>70700</v>
       </c>
-      <c r="G60" s="3">
-        <v>58000</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
+      <c r="H60" s="3">
+        <v>57400</v>
+      </c>
+      <c r="I60" s="3">
+        <v>56700</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
@@ -2498,37 +2637,40 @@
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2545,28 +2687,31 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>1900</v>
+        <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="G62" s="3">
-        <v>10100</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
+        <v>800</v>
+      </c>
+      <c r="H62" s="3">
+        <v>11200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>8800</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
@@ -2574,17 +2719,20 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>15300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,28 +2851,31 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>92700</v>
+        <v>105700</v>
       </c>
       <c r="E66" s="3">
-        <v>72900</v>
+        <v>90500</v>
       </c>
       <c r="F66" s="3">
+        <v>71600</v>
+      </c>
+      <c r="G66" s="3">
         <v>72700</v>
       </c>
-      <c r="G66" s="3">
-        <v>68100</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
+      <c r="H66" s="3">
+        <v>69500</v>
+      </c>
+      <c r="I66" s="3">
+        <v>66600</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
@@ -2726,17 +2883,20 @@
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>16000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2842,16 +3009,16 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>235300</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>230100</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>226900</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -2865,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,28 +3073,31 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-305700</v>
+        <v>-308600</v>
       </c>
       <c r="E72" s="3">
-        <v>-302400</v>
+        <v>-298400</v>
       </c>
       <c r="F72" s="3">
-        <v>-298000</v>
+        <v>-297100</v>
       </c>
       <c r="G72" s="3">
-        <v>-198500</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
+        <v>-298100</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-285300</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-194100</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
@@ -2932,17 +3105,20 @@
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-15200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-19900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-22400</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>49700</v>
+        <v>50500</v>
       </c>
       <c r="E76" s="3">
-        <v>51400</v>
+        <v>48500</v>
       </c>
       <c r="F76" s="3">
+        <v>50500</v>
+      </c>
+      <c r="G76" s="3">
         <v>53300</v>
       </c>
-      <c r="G76" s="3">
-        <v>-197600</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
+      <c r="H76" s="3">
+        <v>51000</v>
+      </c>
+      <c r="I76" s="3">
+        <v>-193300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-183500</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>308900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>304200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>301700</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
-        <v>44926</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>4</v>
+      <c r="J80" s="2">
+        <v>45016</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3300</v>
+        <v>600</v>
       </c>
       <c r="E81" s="3">
-        <v>-4400</v>
+        <v>-3200</v>
       </c>
       <c r="F81" s="3">
-        <v>-129900</v>
+        <v>-4300</v>
       </c>
       <c r="G81" s="3">
-        <v>-25700</v>
+        <v>-4500</v>
       </c>
       <c r="H81" s="3">
-        <v>-39400</v>
+        <v>-7600</v>
       </c>
       <c r="I81" s="3">
-        <v>-18100</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>4</v>
+        <v>-3900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-6400</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3">
         <v>4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,8 +3425,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3239,26 +3437,26 @@
       <c r="E83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
         <v>400</v>
       </c>
-      <c r="G83" s="3">
-        <v>200</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+      <c r="J83" s="3">
+        <v>400</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3266,8 +3464,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,8 +3669,11 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3467,11 +3683,11 @@
       <c r="E89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F89" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-1100</v>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>4</v>
@@ -3485,8 +3701,8 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -3494,8 +3710,11 @@
       <c r="N89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,31 +3729,32 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3548,8 +3768,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,8 +3850,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3635,11 +3864,11 @@
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G94" s="3">
-        <v>2800</v>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
@@ -3662,8 +3891,11 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,31 +3910,32 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3716,8 +3949,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,8 +4072,11 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3841,11 +4086,11 @@
       <c r="E100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F100" s="3">
-        <v>19800</v>
-      </c>
-      <c r="G100" s="3">
-        <v>2800</v>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
@@ -3862,14 +4107,17 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3879,26 +4127,26 @@
       <c r="E101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F101" s="3">
-        <v>300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>300</v>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>4</v>
+      <c r="I101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J101" s="3">
+        <v>2000</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -3906,42 +4154,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>4</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>18100</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>4900</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>CCG</t>
   </si>
@@ -656,108 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>134800</v>
+      </c>
+      <c r="E8" s="3">
         <v>121300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>117200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>109000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>122400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>112800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>114500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>113500</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -765,35 +768,38 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E9" s="3">
         <v>115200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>112800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>104300</v>
       </c>
-      <c r="G9" s="3">
-        <v>116300</v>
-      </c>
       <c r="H9" s="3">
+        <v>115900</v>
+      </c>
+      <c r="I9" s="3">
         <v>107600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>111000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>108600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
@@ -806,35 +812,38 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E10" s="3">
         <v>6100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4700</v>
       </c>
-      <c r="G10" s="3">
-        <v>6100</v>
-      </c>
       <c r="H10" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I10" s="3">
         <v>5300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -847,8 +856,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,35 +876,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
         <v>1400</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1300</v>
       </c>
       <c r="F12" s="3">
         <v>1300</v>
       </c>
       <c r="G12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H12" s="3">
         <v>1700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2900</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
@@ -905,8 +918,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +962,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -978,8 +997,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -987,8 +1006,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1014,7 +1036,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1028,8 +1050,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1067,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E17" s="3">
         <v>122100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>120700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>113400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>129200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>119500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>117800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>120300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3">
         <v>300</v>
-      </c>
-      <c r="N17" s="3">
-        <v>100</v>
       </c>
       <c r="O17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6800</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>-300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,76 +1173,80 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1223,8 +1259,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1238,25 +1277,25 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1264,49 +1303,55 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
         <v>600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6400</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3">
         <v>4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1331,14 +1376,14 @@
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1346,8 +1391,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1435,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6400</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3">
         <v>4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-97000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9400</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1611,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1699,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6400</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1831,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6400</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,81 +1962,85 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E41" s="3">
         <v>18700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20700</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>600</v>
-      </c>
-      <c r="N41" s="3">
-        <v>700</v>
       </c>
       <c r="O41" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E42" s="3">
         <v>9100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3000</v>
-      </c>
-      <c r="H42" s="3">
-        <v>2000</v>
       </c>
       <c r="I42" s="3">
         <v>2000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
+        <v>2000</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1959,40 +2048,43 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E43" s="3">
         <v>106500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>89300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>67000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>65700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>61100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>59100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2000,8 +2092,11 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2026,8 +2121,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2041,40 +2136,43 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E45" s="3">
         <v>6000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
-        <v>100</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
@@ -2082,49 +2180,55 @@
       <c r="O45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>161800</v>
+      </c>
+      <c r="E46" s="3">
         <v>140200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>123400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>106400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>110000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>106300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>88800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2149,14 +2253,14 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>324200</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>324200</v>
@@ -2164,16 +2268,19 @@
       <c r="O47" s="3">
         <v>324200</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>324200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1600</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1700</v>
       </c>
       <c r="F48" s="3">
         <v>1700</v>
@@ -2182,22 +2289,22 @@
         <v>1700</v>
       </c>
       <c r="H48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I48" s="3">
         <v>1400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1700</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2205,40 +2312,43 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E49" s="3">
         <v>13000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12900</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2246,8 +2356,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,25 +2444,28 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1300</v>
       </c>
       <c r="G52" s="3">
         <v>1300</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3">
+        <v>1300</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
@@ -2360,8 +2479,8 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -2369,8 +2488,11 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2532,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>176400</v>
+      </c>
+      <c r="E54" s="3">
         <v>156200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>139000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>126100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>120500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>103400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>324900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>325000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>325100</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,75 +2614,79 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E57" s="3">
         <v>80700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>64300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>38400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>38800</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>500</v>
-      </c>
-      <c r="N57" s="3">
-        <v>300</v>
       </c>
       <c r="O57" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3500</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
@@ -2567,114 +2700,123 @@
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
-        <v>200</v>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N59" s="3">
         <v>200</v>
       </c>
       <c r="O59" s="3">
+        <v>200</v>
+      </c>
+      <c r="P59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>120300</v>
+      </c>
+      <c r="E60" s="3">
         <v>98200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>89000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>69700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>70700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>57400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56700</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E61" s="3">
         <v>6900</v>
-      </c>
-      <c r="E61" s="3">
-        <v>600</v>
       </c>
       <c r="F61" s="3">
         <v>600</v>
       </c>
       <c r="G61" s="3">
+        <v>600</v>
+      </c>
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2690,49 +2832,55 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>800</v>
       </c>
       <c r="G62" s="3">
         <v>800</v>
       </c>
       <c r="H62" s="3">
+        <v>800</v>
+      </c>
+      <c r="I62" s="3">
         <v>11200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>15300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3008,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>127700</v>
+      </c>
+      <c r="E66" s="3">
         <v>105700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>90500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>71600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>72700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>66600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>16000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3015,14 +3182,14 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>230100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>226900</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3035,8 +3202,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3246,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-298000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-308600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-298400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-297100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-298100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-285300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-194100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-15200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-19900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-22400</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3422,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E76" s="3">
         <v>50500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>48500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>50500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>53300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-193300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-183500</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>308900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>304200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>301700</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3510,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6400</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,8 +3623,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3446,20 +3644,20 @@
       <c r="H83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I83" s="3">
-        <v>400</v>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
+      <c r="K83" s="3">
+        <v>400</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3467,8 +3665,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,8 +3885,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3704,8 +3920,8 @@
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -3713,8 +3929,11 @@
       <c r="O89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +3949,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3756,8 +3976,8 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3771,8 +3991,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,8 +4079,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3894,8 +4123,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4143,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3937,8 +4170,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3952,8 +4185,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,8 +4317,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4110,14 +4355,17 @@
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4136,20 +4384,20 @@
       <c r="H101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3">
         <v>1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4157,8 +4405,11 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4183,19 +4434,22 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>4</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>CCG</t>
   </si>
@@ -741,8 +741,8 @@
       <c r="F8" s="3">
         <v>117200</v>
       </c>
-      <c r="G8" s="3">
-        <v>109000</v>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H8" s="3">
         <v>122400</v>
@@ -785,8 +785,8 @@
       <c r="F9" s="3">
         <v>112800</v>
       </c>
-      <c r="G9" s="3">
-        <v>104300</v>
+      <c r="G9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H9" s="3">
         <v>115900</v>
@@ -829,8 +829,8 @@
       <c r="F10" s="3">
         <v>4400</v>
       </c>
-      <c r="G10" s="3">
-        <v>4700</v>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H10" s="3">
         <v>6500</v>
@@ -891,8 +891,8 @@
       <c r="F12" s="3">
         <v>1300</v>
       </c>
-      <c r="G12" s="3">
-        <v>1300</v>
+      <c r="G12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H12" s="3">
         <v>1700</v>
@@ -1024,7 +1024,7 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1082,8 +1082,8 @@
       <c r="F17" s="3">
         <v>120700</v>
       </c>
-      <c r="G17" s="3">
-        <v>113400</v>
+      <c r="G17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H17" s="3">
         <v>129200</v>
@@ -1126,8 +1126,8 @@
       <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-4400</v>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H18" s="3">
         <v>-6900</v>
@@ -1188,8 +1188,8 @@
       <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>100</v>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H20" s="3">
         <v>-2100</v>
@@ -1233,7 +1233,7 @@
         <v>-3300</v>
       </c>
       <c r="G21" s="3">
-        <v>-4500</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-4700</v>
@@ -1276,8 +1276,8 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -1320,8 +1320,8 @@
       <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-4300</v>
+      <c r="G23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H23" s="3">
         <v>-4500</v>
@@ -1364,8 +1364,8 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1452,8 +1452,8 @@
       <c r="F26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-4300</v>
+      <c r="G26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H26" s="3">
         <v>-4500</v>
@@ -1496,8 +1496,8 @@
       <c r="F27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
-        <v>-4300</v>
+      <c r="G27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H27" s="3">
         <v>-4500</v>
@@ -1716,8 +1716,8 @@
       <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-100</v>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H32" s="3">
         <v>2100</v>
@@ -1760,8 +1760,8 @@
       <c r="F33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
-        <v>-4300</v>
+      <c r="G33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H33" s="3">
         <v>-4500</v>
@@ -1848,8 +1848,8 @@
       <c r="F35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
-        <v>-4300</v>
+      <c r="G35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H35" s="3">
         <v>-4500</v>
@@ -1977,8 +1977,8 @@
       <c r="F41" s="3">
         <v>18300</v>
       </c>
-      <c r="G41" s="3">
-        <v>30400</v>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H41" s="3">
         <v>34300</v>
@@ -2022,7 +2022,7 @@
         <v>9800</v>
       </c>
       <c r="G42" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>3000</v>
@@ -2065,8 +2065,8 @@
       <c r="F43" s="3">
         <v>89300</v>
       </c>
-      <c r="G43" s="3">
-        <v>67000</v>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H43" s="3">
         <v>65700</v>
@@ -2153,8 +2153,8 @@
       <c r="F45" s="3">
         <v>4600</v>
       </c>
-      <c r="G45" s="3">
-        <v>7000</v>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H45" s="3">
         <v>6200</v>
@@ -2197,8 +2197,8 @@
       <c r="F46" s="3">
         <v>123400</v>
       </c>
-      <c r="G46" s="3">
-        <v>106400</v>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H46" s="3">
         <v>110000</v>
@@ -2285,8 +2285,8 @@
       <c r="F48" s="3">
         <v>1700</v>
       </c>
-      <c r="G48" s="3">
-        <v>1700</v>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H48" s="3">
         <v>1700</v>
@@ -2329,8 +2329,8 @@
       <c r="F49" s="3">
         <v>12600</v>
       </c>
-      <c r="G49" s="3">
-        <v>12800</v>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H49" s="3">
         <v>13100</v>
@@ -2461,8 +2461,8 @@
       <c r="F52" s="3">
         <v>1200</v>
       </c>
-      <c r="G52" s="3">
-        <v>1300</v>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H52" s="3">
         <v>1300</v>
@@ -2549,8 +2549,8 @@
       <c r="F54" s="3">
         <v>139000</v>
       </c>
-      <c r="G54" s="3">
-        <v>122100</v>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H54" s="3">
         <v>126100</v>
@@ -2629,8 +2629,8 @@
       <c r="F57" s="3">
         <v>64300</v>
       </c>
-      <c r="G57" s="3">
-        <v>44600</v>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H57" s="3">
         <v>44700</v>
@@ -2673,8 +2673,8 @@
       <c r="F58" s="3">
         <v>10800</v>
       </c>
-      <c r="G58" s="3">
-        <v>10900</v>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H58" s="3">
         <v>11200</v>
@@ -2717,8 +2717,8 @@
       <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="G59" s="3">
-        <v>600</v>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H59" s="3">
         <v>2000</v>
@@ -2761,8 +2761,8 @@
       <c r="F60" s="3">
         <v>89000</v>
       </c>
-      <c r="G60" s="3">
-        <v>69700</v>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H60" s="3">
         <v>70700</v>
@@ -2806,7 +2806,7 @@
         <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>800</v>
@@ -2849,8 +2849,8 @@
       <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
-        <v>800</v>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H62" s="3">
         <v>800</v>
@@ -3025,8 +3025,8 @@
       <c r="F66" s="3">
         <v>90500</v>
       </c>
-      <c r="G66" s="3">
-        <v>71600</v>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H66" s="3">
         <v>72700</v>
@@ -3263,8 +3263,8 @@
       <c r="F72" s="3">
         <v>-298400</v>
       </c>
-      <c r="G72" s="3">
-        <v>-297100</v>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H72" s="3">
         <v>-298100</v>
@@ -3439,8 +3439,8 @@
       <c r="F76" s="3">
         <v>48500</v>
       </c>
-      <c r="G76" s="3">
-        <v>50500</v>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H76" s="3">
         <v>53300</v>
@@ -3576,8 +3576,8 @@
       <c r="F81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
-        <v>-4300</v>
+      <c r="G81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H81" s="3">
         <v>-4500</v>

--- a/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>CCG</t>
   </si>
@@ -656,175 +656,188 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="P7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>118800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>116700</v>
+      </c>
+      <c r="F8" s="3">
         <v>94100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>92900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>134800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>121300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>117200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>122400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>112800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>112800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>114500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>113500</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>109700</v>
+      </c>
+      <c r="F9" s="3">
         <v>89500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>88400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>127300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>115200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>112800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>115900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>107600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>107600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>111000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>108600</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
@@ -834,47 +847,53 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F10" s="3">
         <v>4600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>7500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>6100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>4400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>6500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>5300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>4900</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
@@ -884,8 +903,14 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,13 +929,15 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E12" s="3">
         <v>1300</v>
@@ -919,32 +946,32 @@
         <v>1300</v>
       </c>
       <c r="G12" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="H12" s="3">
         <v>1300</v>
       </c>
       <c r="I12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K12" s="3">
         <v>1700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>2900</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
@@ -954,8 +981,14 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,8 +1037,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1045,17 +1084,23 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1090,10 +1135,10 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1104,8 +1149,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,108 +1172,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>118300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>116200</v>
+      </c>
+      <c r="F17" s="3">
         <v>96000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>94800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>135200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>122100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>120700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>129200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>119500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>119500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>117800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>120300</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-6700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-6700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-6800</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1306,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1253,85 +1320,91 @@
         <v>-100</v>
       </c>
       <c r="F20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>2700</v>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R20" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="T20" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-3300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-7600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-6300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1341,8 +1414,14 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1353,96 +1432,108 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-7600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6400</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3">
         <v>4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1476,23 +1567,29 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,108 +1638,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-7600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6400</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3">
         <v>4700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-97000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-97000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-16200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-9400</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3">
         <v>4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1806,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1862,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1918,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,8 +1974,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1853,96 +1992,108 @@
         <v>100</v>
       </c>
       <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-2700</v>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R32" s="3">
         <v>-5000</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-7600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-7600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6400</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3">
         <v>4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,113 +2142,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-7600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-7600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6400</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3">
         <v>4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P38" s="2">
+      <c r="P38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2285,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,158 +2307,178 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20300</v>
+      </c>
+      <c r="F41" s="3">
         <v>20800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>20600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>18700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>18300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>34300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>35700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>35700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>20700</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
         <v>600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>2500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>2500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>4900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>9100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>9800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>3000</v>
-      </c>
-      <c r="J42" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>2000</v>
       </c>
       <c r="L42" s="3">
         <v>2000</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="N42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>163800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>160900</v>
+      </c>
+      <c r="F43" s="3">
         <v>131600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>129900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>134600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>106500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>89300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>65700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>61100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>61100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>59100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2321,11 +2512,11 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2336,108 +2527,126 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F45" s="3">
         <v>4800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>6000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>6200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>6900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>6900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5700</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>100</v>
+      </c>
+      <c r="T45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>193800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>190400</v>
+      </c>
+      <c r="F46" s="3">
         <v>161300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>159200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>161800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>140200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>123400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>110000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>106300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>106300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>88800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3">
         <v>700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2471,123 +2680,141 @@
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
-        <v>324200</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="3">
-        <v>324200</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3">
         <v>324200</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>324200</v>
+      </c>
+      <c r="T47" s="3">
+        <v>324200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1700</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F49" s="3">
         <v>12500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>12300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>12400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>13000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>12600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>13100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>12800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>12800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>12900</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2863,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,35 +2919,41 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F52" s="3">
         <v>4300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>4200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2727,17 +2966,23 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,58 +3031,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>210900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>207200</v>
+      </c>
+      <c r="F54" s="3">
         <v>179300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>177100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>176400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>156200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>139000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>126100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>120500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>120500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>103400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>324900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>325000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>325100</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +3113,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,96 +3135,104 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>118400</v>
+      </c>
+      <c r="F57" s="3">
         <v>95500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>94300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>99400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>80700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>64300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>44700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>38400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>38400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>38800</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>19100</v>
+      </c>
+      <c r="F58" s="3">
         <v>10800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>10700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>10800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>11200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
@@ -2976,144 +3243,162 @@
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>158000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>155200</v>
+      </c>
+      <c r="F60" s="3">
         <v>123300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>121700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>120300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>98200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>89000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>70700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>57400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>57400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>56700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F61" s="3">
         <v>7700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3126,58 +3411,70 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>200</v>
+      </c>
+      <c r="F62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>200</v>
       </c>
       <c r="H62" s="3">
         <v>400</v>
       </c>
       <c r="I62" s="3">
+        <v>200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>11200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>11200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>8800</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3">
         <v>15300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>20300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3523,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3579,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,58 +3635,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>160100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>157300</v>
+      </c>
+      <c r="F66" s="3">
         <v>131700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>130000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>127700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>105700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>90500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>72700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>69500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>69500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>66600</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>16000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>20800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3717,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3769,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3825,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3526,17 +3861,17 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>230100</v>
       </c>
-      <c r="M70" s="3">
+      <c r="O70" s="3">
         <v>226900</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3546,8 +3881,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,58 +3937,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-313500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-308000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-307200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-303300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-298000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-308600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-298400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-298100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-285300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-285300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-194100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-19900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-22400</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +4049,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +4105,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,58 +4161,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>49900</v>
+      </c>
+      <c r="F76" s="3">
         <v>47700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>47100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>48700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>50500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>48500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>53300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>51000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>51000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-193300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-183500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R76" s="3">
         <v>308900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>304200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>301700</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,113 +4273,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P80" s="2">
+      <c r="P80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-7600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-7600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6400</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3">
         <v>4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4416,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4044,8 +4441,8 @@
       <c r="I83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J83" s="3">
-        <v>400</v>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
@@ -4053,26 +4450,32 @@
       <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="O83" s="3">
+        <v>400</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4524,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4580,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4636,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4692,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,23 +4748,29 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>4</v>
       </c>
@@ -4362,17 +4795,23 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,8 +4830,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4402,11 +4843,11 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>4</v>
@@ -4426,11 +4867,11 @@
       <c r="M91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -4441,8 +4882,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4938,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,23 +4994,29 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F94" s="3">
         <v>1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>1200</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
       </c>
@@ -4591,8 +5050,14 @@
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +5076,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4646,11 +5113,11 @@
       <c r="M96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4661,8 +5128,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +5184,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5240,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,23 +5296,29 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>700</v>
+      </c>
+      <c r="F100" s="3">
         <v>3100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3100</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
       </c>
@@ -4855,14 +5346,20 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4884,8 +5381,8 @@
       <c r="I101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J101" s="3">
-        <v>1900</v>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>4</v>
@@ -4893,41 +5390,47 @@
       <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F102" s="3">
         <v>3700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3700</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -4946,19 +5449,25 @@
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>
